--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N83_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N83_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>89.17864396412132</v>
+        <v>14.49152964416971</v>
       </c>
       <c r="D2" t="n">
-        <v>73.37316258451941</v>
+        <v>11.9231389199844</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
